--- a/data/trans_orig/IP18A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46611</t>
+          <t>46582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98616</t>
+          <t>98601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63399</t>
+          <t>61853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131275</t>
+          <t>130834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117571</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241907</t>
+          <t>241380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115747</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127548</t>
+          <t>127569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132897</t>
+          <t>132882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245970</t>
+          <t>246035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252627</t>
+          <t>252831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>589231</t>
+          <t>588920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>595987</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>615442</t>
+          <t>615496</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>622634</t>
+          <t>622842</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1208191</t>
+          <t>1207998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1217666</t>
+          <t>1217490</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92621</t>
+          <t>91953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190098</t>
+          <t>190140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63324</t>
+          <t>63998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65063</t>
+          <t>65641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70598</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>132050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>137922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75804</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146929</t>
+          <t>147406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51904</t>
+          <t>51975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58343</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>104324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112078</t>
+          <t>112120</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129561</t>
+          <t>129740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139748</t>
+          <t>139385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>271862</t>
+          <t>271843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276807</t>
+          <t>276808</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147429</t>
+          <t>147135</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154578</t>
+          <t>154689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304352</t>
+          <t>304916</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310585</t>
+          <t>310604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>653426</t>
+          <t>653253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>661605</t>
+          <t>661085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>692943</t>
+          <t>692947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>702690</t>
+          <t>702844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1350603</t>
+          <t>1349887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1362056</t>
+          <t>1362207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,47 +7737,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9618</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1635</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9420</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77913</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85328</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,49 +7850,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>88501</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>83435</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91104</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>97,91%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88501</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83633</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91418</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>255</t>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164971</t>
+          <t>165875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>176040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>58932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124901</t>
+          <t>124580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69423</t>
+          <t>69782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148853</t>
+          <t>148961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104615</t>
+          <t>105356</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110935</t>
+          <t>110900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>102564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111330</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>210839</t>
+          <t>211416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220746</t>
+          <t>221013</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>627562</t>
+          <t>627299</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>636592</t>
+          <t>636653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>653510</t>
+          <t>653672</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>664151</t>
+          <t>664668</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1284552</t>
+          <t>1284980</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1298611</t>
+          <t>1299068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27111</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48879</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>99164</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129359</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>216887</t>
+          <t>217059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227523</t>
+          <t>227611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
